--- a/RTD_Test.xlsx
+++ b/RTD_Test.xlsx
@@ -455,279 +455,279 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03487700306325836</v>
+        <v>0.3490544071046404</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8151636450588776</v>
+        <v>0.248259670783146</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5868011231460354</v>
+        <v>0.5774373374740988</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.000609874725342</v>
+        <v>1.000751256942749</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3194733442368885</v>
+        <v>0.5017719482287086</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4040675815606316</v>
+        <v>0.4760406816191802</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5220057152128563</v>
+        <v>0.4917973874570435</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.500920534133911</v>
+        <v>1.501152992248535</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7862994164405781</v>
+        <v>0.8299709172122618</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5244421641713455</v>
+        <v>0.5030012914752875</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5701152091668368</v>
+        <v>0.4719191492574409</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2.001511812210083</v>
+        <v>2.001639127731323</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4530559570747237</v>
+        <v>0.5833425027880423</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3705016889657767</v>
+        <v>0.3547339339900626</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3141214092736647</v>
+        <v>0.4741822826102145</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2.50166654586792</v>
+        <v>2.502125024795532</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2946799183020466</v>
+        <v>0.3893589532834008</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7011440139142888</v>
+        <v>0.3714115705369924</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4861926751137037</v>
+        <v>0.4764308218970495</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3.002222537994385</v>
+        <v>3.002729654312134</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5046237689505204</v>
+        <v>0.4227423181441473</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6067422960205471</v>
+        <v>0.6880725263558857</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6447231160585563</v>
+        <v>0.5971702147486307</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3.502471685409546</v>
+        <v>3.503304719924927</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4611076016211428</v>
+        <v>0.647018590387954</v>
       </c>
       <c r="C8" t="n">
-        <v>0.66971188706283</v>
+        <v>0.517859424420221</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5433282722813196</v>
+        <v>0.3245220764300805</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4.002974271774292</v>
+        <v>4.003474950790405</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6742020955146317</v>
+        <v>0.4593404184807229</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4382354542855996</v>
+        <v>0.3773285412939802</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6278772112414522</v>
+        <v>0.5295368539614567</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4.503096342086792</v>
+        <v>4.503752708435059</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4200425179502899</v>
+        <v>0.7072980470754077</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4325246794586685</v>
+        <v>0.6812024448589786</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4131625774570534</v>
+        <v>0.4929870425356312</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5.003192663192749</v>
+        <v>5.004355430603027</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5715571835961711</v>
+        <v>0.2454954235273817</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5530946679886033</v>
+        <v>0.3245287455652583</v>
       </c>
       <c r="D11" t="n">
-        <v>0.589282330812718</v>
+        <v>0.4979329460379905</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5.50358510017395</v>
+        <v>5.504878759384155</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4626092737446066</v>
+        <v>0.5866312255825227</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4324223695529558</v>
+        <v>0.4078486354594547</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5446444066100353</v>
+        <v>0.4799655265521554</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6.004073858261108</v>
+        <v>6.004993438720703</v>
       </c>
       <c r="B13" t="n">
-        <v>0.754181480259843</v>
+        <v>0.5922079552211313</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4724230850480381</v>
+        <v>0.7025772466078609</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4869473497688139</v>
+        <v>0.668913124301212</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6.504162311553955</v>
+        <v>6.505269765853882</v>
       </c>
       <c r="B14" t="n">
-        <v>0.4653392278716948</v>
+        <v>0.6167244192170167</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4635322455506438</v>
+        <v>0.8158560636702392</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5641564648955297</v>
+        <v>0.468293403783368</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7.004342794418335</v>
+        <v>7.005335330963135</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5398987133615794</v>
+        <v>0.4238503242351624</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4335270483189417</v>
+        <v>0.627386149022955</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3076209254553325</v>
+        <v>0.2588738134813354</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7.504696846008301</v>
+        <v>7.505620241165161</v>
       </c>
       <c r="B16" t="n">
-        <v>0.6155166016514894</v>
+        <v>0.4416609054080249</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6483283243064742</v>
+        <v>0.3404637461556385</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3369649170170312</v>
+        <v>0.594447368654775</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>8.005099534988403</v>
+        <v>8.006086826324463</v>
       </c>
       <c r="B17" t="n">
-        <v>0.7388570994996744</v>
+        <v>0.6127709853193541</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5553675633553771</v>
+        <v>0.5543642027234184</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6226679441722945</v>
+        <v>0.6412208611115039</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8.505716562271118</v>
+        <v>8.506195068359375</v>
       </c>
       <c r="B18" t="n">
-        <v>0.359320828089959</v>
+        <v>0.5819928279394457</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5082839046695312</v>
+        <v>0.6206374221750824</v>
       </c>
       <c r="D18" t="n">
-        <v>0.417213386127731</v>
+        <v>0.5215350201578198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9.006170749664307</v>
+        <v>9.006816387176514</v>
       </c>
       <c r="B19" t="n">
-        <v>0.2894928985913553</v>
+        <v>0.3177073083154384</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6740963843161845</v>
+        <v>0.5793499567038479</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4265809300961557</v>
+        <v>0.5457633945189517</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>9.506727695465088</v>
+        <v>9.507410049438477</v>
       </c>
       <c r="B20" t="n">
-        <v>0.4698639922981291</v>
+        <v>0.3345052587447143</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4126803927840239</v>
+        <v>0.6117611325189956</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3343036507914621</v>
+        <v>0.5532375927984332</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10.00699996948242</v>
+        <v>10.00792098045349</v>
       </c>
       <c r="B21" t="n">
-        <v>0.5177566929910961</v>
+        <v>0.7599250400633278</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5600021537557388</v>
+        <v>0.4429727898916484</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4549661946642523</v>
+        <v>0.6003729628778598</v>
       </c>
     </row>
   </sheetData>
